--- a/data/trans_camb/P19C03-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P19C03-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 2,85</t>
+          <t>-6,04; 2,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 3,38</t>
+          <t>-5,98; 3,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,09; -2,09</t>
+          <t>-11,0; -2,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 4,95</t>
+          <t>-2,68; 4,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 3,68</t>
+          <t>-4,4; 3,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,12; -4,99</t>
+          <t>-11,71; -5,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 2,46</t>
+          <t>-2,59; 3,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 2,42</t>
+          <t>-4,13; 2,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,08; -4,87</t>
+          <t>-10,13; -4,71</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-26,16; 16,19</t>
+          <t>-25,82; 12,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-25,75; 17,29</t>
+          <t>-26,46; 19,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-47,04; -10,92</t>
+          <t>-46,44; -10,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 23,28</t>
+          <t>-11,05; 23,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-19,39; 17,68</t>
+          <t>-17,96; 17,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-48,52; -23,47</t>
+          <t>-47,4; -24,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,06; 12,04</t>
+          <t>-11,19; 15,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-17,6; 11,56</t>
+          <t>-17,45; 10,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-42,68; -23,04</t>
+          <t>-42,87; -22,95</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 0,5</t>
+          <t>-6,95; 0,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,68; -3,49</t>
+          <t>-10,63; -3,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-25,06; -14,43</t>
+          <t>-24,97; -14,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,06; -1,94</t>
+          <t>-8,86; -1,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,21; -6,36</t>
+          <t>-12,81; -6,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-25,75; -15,47</t>
+          <t>-26,86; -16,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,76; -1,65</t>
+          <t>-6,82; -1,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,12; -6,11</t>
+          <t>-11,07; -6,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-23,99; -16,14</t>
+          <t>-23,54; -16,11</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,23; 1,23</t>
+          <t>-17,16; 1,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-27,05; -9,88</t>
+          <t>-26,9; -10,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-65,76; -39,87</t>
+          <t>-65,03; -40,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,69; -5,05</t>
+          <t>-21,86; -4,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-32,81; -17,11</t>
+          <t>-31,39; -17,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-65,05; -41,77</t>
+          <t>-65,63; -42,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,13; -4,5</t>
+          <t>-16,92; -4,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-28,06; -16,49</t>
+          <t>-28,21; -17,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-61,93; -43,88</t>
+          <t>-60,88; -43,3</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 7,51</t>
+          <t>-6,16; 6,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,47; -0,01</t>
+          <t>-12,06; -0,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,31; -9,01</t>
+          <t>-20,1; -8,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 1,76</t>
+          <t>-11,67; 1,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,93; -3,6</t>
+          <t>-15,12; -3,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,29; -7,75</t>
+          <t>-18,38; -7,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 2,21</t>
+          <t>-6,68; 2,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,61; -4,09</t>
+          <t>-12,28; -3,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-17,79; -9,9</t>
+          <t>-18,07; -10,19</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-16,64; 27,01</t>
+          <t>-16,91; 23,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-35,36; 0,38</t>
+          <t>-34,94; -1,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-58,95; -32,48</t>
+          <t>-58,9; -31,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-32,23; 6,17</t>
+          <t>-33,54; 4,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-43,62; -13,3</t>
+          <t>-43,04; -10,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-52,41; -28,56</t>
+          <t>-52,26; -27,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-21,06; 7,68</t>
+          <t>-20,15; 7,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-36,52; -13,43</t>
+          <t>-36,19; -12,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-52,34; -34,22</t>
+          <t>-52,62; -34,95</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 0,69</t>
+          <t>-4,39; 0,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,91; -1,74</t>
+          <t>-7,11; -1,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,36; -11,16</t>
+          <t>-18,82; -11,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,62; -0,84</t>
+          <t>-5,66; -0,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,32; -3,38</t>
+          <t>-8,34; -3,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,08; -11,3</t>
+          <t>-17,78; -11,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,3; -0,7</t>
+          <t>-4,37; -0,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,0; -3,37</t>
+          <t>-6,9; -3,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-16,77; -12,18</t>
+          <t>-16,94; -12,09</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 2,22</t>
+          <t>-13,17; 2,21</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-20,73; -5,63</t>
+          <t>-21,31; -6,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-56,59; -35,95</t>
+          <t>-57,24; -36,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-16,9; -2,88</t>
+          <t>-16,73; -2,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,99; -10,85</t>
+          <t>-24,87; -10,82</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-55,04; -36,51</t>
+          <t>-54,55; -37,21</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-12,85; -2,22</t>
+          <t>-13,18; -2,33</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-21,05; -10,83</t>
+          <t>-21,19; -11,26</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-51,82; -38,76</t>
+          <t>-52,15; -38,65</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C03-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P19C03-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-6,45</t>
+          <t>-5,71</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-7,49</t>
+          <t>-7,18</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 2,37</t>
+          <t>-5,8; 2,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 3,88</t>
+          <t>-6,3; 3,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,0; -2,03</t>
+          <t>-10,03; -1,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 4,85</t>
+          <t>-3,08; 4,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 3,74</t>
+          <t>-4,89; 4,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,71; -5,03</t>
+          <t>-11,29; -4,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 3,07</t>
+          <t>-3,12; 2,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 2,24</t>
+          <t>-3,99; 2,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,13; -4,71</t>
+          <t>-9,89; -4,24</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-30,27%</t>
+          <t>-26,8%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-36,13%</t>
+          <t>-36,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-33,8%</t>
+          <t>-32,42%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-25,82; 12,61</t>
+          <t>-25,2; 13,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-26,46; 19,97</t>
+          <t>-26,73; 16,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-46,44; -10,78</t>
+          <t>-44,4; -6,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 23,03</t>
+          <t>-12,13; 22,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-17,96; 17,78</t>
+          <t>-19,67; 18,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-47,4; -24,34</t>
+          <t>-46,11; -21,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-11,19; 15,16</t>
+          <t>-13,31; 12,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-17,45; 10,8</t>
+          <t>-17,27; 10,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-42,87; -22,95</t>
+          <t>-42,0; -20,53</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-18,67</t>
+          <t>-16,59</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-20,58</t>
+          <t>-19,42</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-19,63</t>
+          <t>-18,01</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 0,4</t>
+          <t>-7,07; -0,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,63; -3,92</t>
+          <t>-11,16; -4,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-24,97; -14,51</t>
+          <t>-19,77; -12,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,86; -1,61</t>
+          <t>-8,9; -1,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,81; -6,2</t>
+          <t>-13,4; -6,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,86; -16,29</t>
+          <t>-22,88; -16,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,82; -1,79</t>
+          <t>-6,47; -1,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,07; -6,28</t>
+          <t>-10,85; -6,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-23,54; -16,11</t>
+          <t>-20,19; -15,6</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-49,57%</t>
+          <t>-44,06%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-53,12%</t>
+          <t>-50,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-51,38%</t>
+          <t>-47,14%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,16; 1,15</t>
+          <t>-17,52; -0,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-26,9; -10,57</t>
+          <t>-28,37; -11,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-65,03; -40,16</t>
+          <t>-50,02; -36,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,86; -4,47</t>
+          <t>-21,81; -3,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,39; -17,0</t>
+          <t>-32,94; -17,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-65,63; -42,77</t>
+          <t>-55,97; -44,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,92; -4,63</t>
+          <t>-16,41; -4,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-28,21; -17,18</t>
+          <t>-27,74; -16,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-60,88; -43,3</t>
+          <t>-51,07; -42,29</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-14,96</t>
+          <t>-15,71</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-13,09</t>
+          <t>-11,9</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-14,02</t>
+          <t>-13,78</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 6,58</t>
+          <t>-5,51; 6,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,06; -0,21</t>
+          <t>-12,35; -0,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,1; -8,54</t>
+          <t>-21,35; -10,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 1,26</t>
+          <t>-11,18; 1,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,12; -3,0</t>
+          <t>-15,95; -3,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,38; -7,73</t>
+          <t>-17,09; -6,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 2,38</t>
+          <t>-6,88; 2,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,28; -3,6</t>
+          <t>-12,47; -3,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-18,07; -10,19</t>
+          <t>-17,88; -10,22</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-47,07%</t>
+          <t>-49,45%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-41,64%</t>
+          <t>-37,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-44,35%</t>
+          <t>-43,6%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 23,63</t>
+          <t>-16,23; 23,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-34,94; -1,07</t>
+          <t>-35,83; -2,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-58,9; -31,65</t>
+          <t>-60,24; -35,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-33,54; 4,41</t>
+          <t>-33,19; 5,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-43,04; -10,83</t>
+          <t>-44,28; -12,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-52,26; -27,48</t>
+          <t>-49,17; -24,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-20,15; 7,76</t>
+          <t>-20,53; 9,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-36,19; -12,35</t>
+          <t>-36,4; -13,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-52,62; -34,95</t>
+          <t>-51,6; -34,64</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-14,01</t>
+          <t>-12,83</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-14,6</t>
+          <t>-13,73</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-14,31</t>
+          <t>-13,3</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 0,68</t>
+          <t>-4,52; 0,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,11; -1,88</t>
+          <t>-7,2; -1,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,82; -11,25</t>
+          <t>-15,39; -10,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,66; -0,66</t>
+          <t>-5,5; -0,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,34; -3,34</t>
+          <t>-8,46; -3,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-17,78; -11,61</t>
+          <t>-15,73; -11,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,37; -0,74</t>
+          <t>-4,27; -0,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,9; -3,52</t>
+          <t>-6,92; -3,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-16,94; -12,09</t>
+          <t>-14,81; -11,7</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-43,79%</t>
+          <t>-40,11%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-45,53%</t>
+          <t>-42,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-44,69%</t>
+          <t>-41,52%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-13,17; 2,21</t>
+          <t>-13,49; 2,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-21,31; -6,03</t>
+          <t>-21,38; -5,56</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-57,24; -36,25</t>
+          <t>-46,19; -34,22</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-16,73; -2,14</t>
+          <t>-16,56; -1,67</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,87; -10,82</t>
+          <t>-25,37; -10,84</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-54,55; -37,21</t>
+          <t>-47,45; -37,58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-13,18; -2,33</t>
+          <t>-12,96; -2,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-21,19; -11,26</t>
+          <t>-20,81; -10,75</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-52,15; -38,65</t>
+          <t>-44,88; -37,42</t>
         </is>
       </c>
     </row>
